--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="506">
   <si>
     <t>Filename</t>
   </si>
@@ -808,742 +808,730 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9703,0.0004,0.0019,0.0098</t>
-  </si>
-  <si>
-    <t>0.3511,0.0001,0.0025,0.7517</t>
-  </si>
-  <si>
-    <t>0.9766,0.0001,0.0000,0.0135</t>
-  </si>
-  <si>
-    <t>0.8482,0.0003,0.0002,0.1175</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9368,0.0009,0.0012,0.0229</t>
+  </si>
+  <si>
+    <t>0.3813,0.0002,0.0011,0.7282</t>
+  </si>
+  <si>
+    <t>0.9572,0.0001,0.0000,0.0183</t>
+  </si>
+  <si>
+    <t>0.8842,0.0003,0.0002,0.0791</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9981,0.0001,0.0000,0.0003</t>
+    <t>0.9993,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0000,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9845,0.0002,0.0000,0.0039</t>
-  </si>
-  <si>
-    <t>0.9980,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9837,0.0006,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.0151,0.0007,0.9873,0.0010</t>
-  </si>
-  <si>
-    <t>0.8262,0.0006,0.2661,0.0011</t>
-  </si>
-  <si>
-    <t>0.2097,0.0018,0.7874,0.0102</t>
-  </si>
-  <si>
-    <t>0.9551,0.0010,0.0108,0.0088</t>
+    <t>0.9606,0.0002,0.0277,0.0020</t>
+  </si>
+  <si>
+    <t>0.0068,0.0020,0.9935,0.0007</t>
+  </si>
+  <si>
+    <t>0.6710,0.0009,0.4737,0.0008</t>
+  </si>
+  <si>
+    <t>0.2705,0.0017,0.7171,0.0135</t>
+  </si>
+  <si>
+    <t>0.9737,0.0009,0.0117,0.0022</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0018,0.9947,0.0004,0.0011</t>
-  </si>
-  <si>
-    <t>0.1280,0.2906,0.0005,0.0729</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9716,0.0002,0.0186,0.0008</t>
-  </si>
-  <si>
-    <t>0.9230,0.0004,0.0778,0.0016</t>
-  </si>
-  <si>
-    <t>0.5865,0.0003,0.5569,0.0015</t>
-  </si>
-  <si>
-    <t>0.5777,0.0005,0.5718,0.0010</t>
-  </si>
-  <si>
-    <t>0.0156,0.0001,0.9863,0.0007</t>
-  </si>
-  <si>
-    <t>0.7771,0.0001,0.3368,0.0009</t>
-  </si>
-  <si>
-    <t>0.0364,0.0001,0.9730,0.0005</t>
-  </si>
-  <si>
-    <t>0.6997,0.2025,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9658,0.0078,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0008</t>
-  </si>
-  <si>
-    <t>0.2621,0.6377,0.0440,0.0013</t>
-  </si>
-  <si>
-    <t>0.9792,0.0047,0.0012,0.0023</t>
-  </si>
-  <si>
-    <t>0.9949,0.0008,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.8674,0.1312,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.0580,0.9364,0.0208,0.0011</t>
-  </si>
-  <si>
-    <t>0.5264,0.0329,0.4269,0.0034</t>
-  </si>
-  <si>
-    <t>0.7528,0.0112,0.1994,0.0144</t>
-  </si>
-  <si>
-    <t>0.8087,0.0012,0.2438,0.0028</t>
-  </si>
-  <si>
-    <t>0.9207,0.0001,0.0941,0.0008</t>
-  </si>
-  <si>
-    <t>0.1150,0.0115,0.8894,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0028,0.0000</t>
-  </si>
-  <si>
-    <t>0.1790,0.0001,0.8520,0.0010</t>
-  </si>
-  <si>
-    <t>0.1304,0.0037,0.0001,0.7937</t>
-  </si>
-  <si>
-    <t>0.0013,0.9726,0.0005,0.1738</t>
-  </si>
-  <si>
-    <t>0.0002,0.9982,0.0007,0.0077</t>
-  </si>
-  <si>
-    <t>0.0010,0.9984,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0373,0.0751,0.8637,0.0015</t>
-  </si>
-  <si>
-    <t>0.2505,0.0428,0.7085,0.0058</t>
-  </si>
-  <si>
-    <t>0.5559,0.0017,0.4363,0.0229</t>
-  </si>
-  <si>
-    <t>0.3565,0.0001,0.6909,0.0033</t>
-  </si>
-  <si>
-    <t>0.0285,0.0002,0.9832,0.0002</t>
-  </si>
-  <si>
-    <t>0.0583,0.0015,0.9105,0.0120</t>
-  </si>
-  <si>
-    <t>0.9953,0.0004,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9968,0.0005,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0029,0.9970,0.0009</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0002,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9973,0.0005,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0094,0.9542,0.1948,0.0020</t>
-  </si>
-  <si>
-    <t>0.2924,0.0158,0.7044,0.0054</t>
-  </si>
-  <si>
-    <t>0.2983,0.0016,0.7546,0.0013</t>
-  </si>
-  <si>
-    <t>0.0011,0.9041,0.8975,0.0002</t>
-  </si>
-  <si>
-    <t>0.0061,0.0003,0.9918,0.0003</t>
-  </si>
-  <si>
-    <t>0.0037,0.9929,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9853,0.0032,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.9476,0.0116,0.0151,0.0027</t>
-  </si>
-  <si>
-    <t>0.0038,0.0012,0.9969,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.9927,0.6574,0.0001</t>
-  </si>
-  <si>
-    <t>0.0333,0.8610,0.1957,0.0007</t>
-  </si>
-  <si>
-    <t>0.0018,0.9950,0.0091,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.9791,0.4037,0.0006</t>
-  </si>
-  <si>
-    <t>0.1507,0.0001,0.0008,0.9247</t>
-  </si>
-  <si>
-    <t>0.1026,0.0001,0.0003,0.9708</t>
-  </si>
-  <si>
-    <t>0.2304,0.0001,0.0005,0.8865</t>
-  </si>
-  <si>
-    <t>0.1451,0.0002,0.0001,0.9142</t>
-  </si>
-  <si>
-    <t>0.0989,0.0000,0.0001,0.9699</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0107,0.9522,0.1888,0.0025</t>
-  </si>
-  <si>
-    <t>0.0227,0.8342,0.2848,0.0005</t>
-  </si>
-  <si>
-    <t>0.0032,0.9896,0.0247,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.9790,0.1662,0.0018</t>
-  </si>
-  <si>
-    <t>0.0043,0.9322,0.5440,0.0003</t>
-  </si>
-  <si>
-    <t>0.0375,0.7600,0.4031,0.0022</t>
-  </si>
-  <si>
-    <t>0.9974,0.0003,0.0000,0.0002</t>
+    <t>0.0007,0.9974,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.1593,0.5706,0.0005,0.0087</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9606,0.0007,0.0323,0.0006</t>
+  </si>
+  <si>
+    <t>0.7523,0.0002,0.2450,0.0065</t>
+  </si>
+  <si>
+    <t>0.3503,0.0003,0.7527,0.0018</t>
+  </si>
+  <si>
+    <t>0.2807,0.0006,0.7312,0.0065</t>
+  </si>
+  <si>
+    <t>0.0493,0.0006,0.9525,0.0023</t>
+  </si>
+  <si>
+    <t>0.5069,0.0001,0.5504,0.0025</t>
+  </si>
+  <si>
+    <t>0.0351,0.0001,0.9727,0.0005</t>
+  </si>
+  <si>
+    <t>0.7749,0.1660,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9802,0.0013,0.0009,0.0025</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9995,0.0013</t>
+  </si>
+  <si>
+    <t>0.0393,0.9313,0.0310,0.0011</t>
+  </si>
+  <si>
+    <t>0.9886,0.0019,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9772,0.0018,0.0014,0.0041</t>
+  </si>
+  <si>
+    <t>0.9317,0.0356,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.1898,0.8081,0.0129,0.0031</t>
+  </si>
+  <si>
+    <t>0.3074,0.3640,0.1269,0.0056</t>
+  </si>
+  <si>
+    <t>0.8049,0.0008,0.2526,0.0032</t>
+  </si>
+  <si>
+    <t>0.8126,0.0007,0.2309,0.0037</t>
+  </si>
+  <si>
+    <t>0.7294,0.0001,0.2879,0.0036</t>
+  </si>
+  <si>
+    <t>0.2534,0.0063,0.7894,0.0010</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0052,0.0000</t>
+  </si>
+  <si>
+    <t>0.2316,0.0003,0.7998,0.0031</t>
+  </si>
+  <si>
+    <t>0.0923,0.0023,0.0000,0.8436</t>
+  </si>
+  <si>
+    <t>0.0014,0.9804,0.0007,0.1260</t>
+  </si>
+  <si>
+    <t>0.0012,0.9964,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.9986,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.0098,0.0498,0.9468,0.0006</t>
+  </si>
+  <si>
+    <t>0.0211,0.3564,0.8815,0.0015</t>
+  </si>
+  <si>
+    <t>0.2567,0.0007,0.7803,0.0055</t>
+  </si>
+  <si>
+    <t>0.0932,0.0001,0.9073,0.0045</t>
+  </si>
+  <si>
+    <t>0.0229,0.0002,0.9843,0.0004</t>
+  </si>
+  <si>
+    <t>0.1074,0.0003,0.9201,0.0011</t>
+  </si>
+  <si>
+    <t>0.9976,0.0002,0.0000,0.0002</t>
   </si>
   <si>
     <t>0.9986,0.0003,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9896,0.0001,0.0000,0.0038</t>
+    <t>0.9992,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0008,0.9958,0.0008</t>
+  </si>
+  <si>
+    <t>0.9981,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0009,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0288,0.6178,0.6868,0.0018</t>
+  </si>
+  <si>
+    <t>0.2181,0.0025,0.8147,0.0020</t>
+  </si>
+  <si>
+    <t>0.1092,0.0093,0.8806,0.0021</t>
+  </si>
+  <si>
+    <t>0.0091,0.8354,0.6619,0.0006</t>
+  </si>
+  <si>
+    <t>0.0080,0.0001,0.9915,0.0003</t>
+  </si>
+  <si>
+    <t>0.0104,0.9843,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.9986,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9480,0.0027,0.0297,0.0095</t>
+  </si>
+  <si>
+    <t>0.4242,0.0128,0.6227,0.0081</t>
+  </si>
+  <si>
+    <t>0.0045,0.0019,0.9966,0.0009</t>
+  </si>
+  <si>
+    <t>0.0021,0.9760,0.2690,0.0003</t>
+  </si>
+  <si>
+    <t>0.0090,0.9659,0.0913,0.0003</t>
+  </si>
+  <si>
+    <t>0.0046,0.9865,0.0222,0.0035</t>
+  </si>
+  <si>
+    <t>0.0020,0.8860,0.6894,0.0009</t>
+  </si>
+  <si>
+    <t>0.4218,0.0000,0.0009,0.6569</t>
+  </si>
+  <si>
+    <t>0.0874,0.0001,0.0002,0.9727</t>
+  </si>
+  <si>
+    <t>0.3891,0.0001,0.0004,0.7220</t>
+  </si>
+  <si>
+    <t>0.3860,0.0003,0.0001,0.5992</t>
+  </si>
+  <si>
+    <t>0.0425,0.0000,0.0003,0.9889</t>
+  </si>
+  <si>
+    <t>0.0054,0.0001,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.0055,0.9713,0.2037,0.0009</t>
+  </si>
+  <si>
+    <t>0.0193,0.8397,0.2582,0.0003</t>
+  </si>
+  <si>
+    <t>0.0454,0.7548,0.2096,0.0120</t>
+  </si>
+  <si>
+    <t>0.0088,0.8828,0.3447,0.0037</t>
+  </si>
+  <si>
+    <t>0.0149,0.7783,0.5667,0.0005</t>
+  </si>
+  <si>
+    <t>0.2153,0.2490,0.4592,0.0033</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9917,0.0006,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9824,0.0001,0.0000,0.0072</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0003,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0099,0.0001,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.5077,0.0012,0.5383,0.0085</t>
+  </si>
+  <si>
+    <t>0.9865,0.0004,0.0038,0.0004</t>
+  </si>
+  <si>
+    <t>0.1469,0.0005,0.8952,0.0015</t>
+  </si>
+  <si>
+    <t>0.0033,0.9863,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.0018,0.9955,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0331,0.6894,0.0000,0.0067</t>
+  </si>
+  <si>
+    <t>0.0160,0.9101,0.0005,0.0179</t>
+  </si>
+  <si>
+    <t>0.0027,0.9960,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9969,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.6833,0.1278,0.0002,0.0038</t>
+  </si>
+  <si>
+    <t>0.7132,0.0057,0.2339,0.0411</t>
+  </si>
+  <si>
+    <t>0.8307,0.0002,0.2563,0.0011</t>
+  </si>
+  <si>
+    <t>0.9776,0.0008,0.0040,0.0016</t>
+  </si>
+  <si>
+    <t>0.9760,0.0014,0.0076,0.0007</t>
+  </si>
+  <si>
+    <t>0.0287,0.0007,0.0013,0.9868</t>
+  </si>
+  <si>
+    <t>0.0014,0.9948,0.0016,0.0037</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.9993,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0189,0.7948,0.7275,0.0077</t>
+  </si>
+  <si>
+    <t>0.0661,0.9502,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9536,0.0143,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9910,0.0033,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9951,0.0001,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9903,0.0091,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0001,0.0000,0.0010</t>
   </si>
   <si>
     <t>0.9989,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9983,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0005,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9984,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0050,0.0001,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0140,0.0004,0.9800,0.0036</t>
-  </si>
-  <si>
-    <t>0.9863,0.0004,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.0605,0.0002,0.9600,0.0010</t>
-  </si>
-  <si>
-    <t>0.0040,0.9792,0.0001,0.0026</t>
-  </si>
-  <si>
-    <t>0.0024,0.9948,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.0464,0.6125,0.0001,0.0103</t>
-  </si>
-  <si>
-    <t>0.0307,0.8553,0.0002,0.0078</t>
-  </si>
-  <si>
-    <t>0.0007,0.9986,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9989,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.6843,0.0736,0.0002,0.0098</t>
-  </si>
-  <si>
-    <t>0.9253,0.0024,0.0043,0.0175</t>
-  </si>
-  <si>
-    <t>0.7844,0.0004,0.2698,0.0029</t>
-  </si>
-  <si>
-    <t>0.9472,0.0014,0.0248,0.0042</t>
-  </si>
-  <si>
-    <t>0.9082,0.0041,0.0718,0.0038</t>
-  </si>
-  <si>
-    <t>0.0230,0.0010,0.0011,0.9896</t>
-  </si>
-  <si>
-    <t>0.0027,0.9948,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.9976,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0086,0.8963,0.7620,0.0041</t>
-  </si>
-  <si>
-    <t>0.0176,0.9792,0.0015,0.0004</t>
-  </si>
-  <si>
-    <t>0.9455,0.0151,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9885,0.0046,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9981,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0001,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9968,0.0025,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9976,0.0000,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.1580,0.0397,0.8170,0.0052</t>
-  </si>
-  <si>
-    <t>0.4540,0.0158,0.5589,0.0007</t>
-  </si>
-  <si>
-    <t>0.1333,0.0020,0.8977,0.0004</t>
-  </si>
-  <si>
-    <t>0.4996,0.0180,0.5235,0.0023</t>
-  </si>
-  <si>
-    <t>0.9903,0.0003,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9798,0.0002,0.0095,0.0015</t>
-  </si>
-  <si>
-    <t>0.7112,0.0004,0.3111,0.0063</t>
-  </si>
-  <si>
-    <t>0.9396,0.0022,0.0267,0.0035</t>
-  </si>
-  <si>
-    <t>0.4904,0.0001,0.0000,0.4963</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0027,0.0003,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0161,0.0000,0.0001,0.9966</t>
-  </si>
-  <si>
-    <t>0.0073,0.8756,0.6653,0.0006</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0199,0.9383,0.0001,0.0031</t>
-  </si>
-  <si>
-    <t>0.9989,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9727,0.0095,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9966,0.0003,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9144,0.0000,0.0000,0.1087</t>
-  </si>
-  <si>
-    <t>0.3178,0.0047,0.6797,0.0195</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9068,0.0342,0.0049,0.0062</t>
-  </si>
-  <si>
-    <t>0.9852,0.0029,0.0004,0.0015</t>
-  </si>
-  <si>
-    <t>0.9872,0.0035,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.8609,0.0041,0.0938,0.0131</t>
-  </si>
-  <si>
-    <t>0.9011,0.0175,0.0010,0.0127</t>
-  </si>
-  <si>
-    <t>0.9843,0.0026,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0001,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0001,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8961,0.0313,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9197,0.0113,0.0002,0.0055</t>
-  </si>
-  <si>
-    <t>0.9705,0.0039,0.0001,0.0022</t>
-  </si>
-  <si>
-    <t>0.9628,0.0038,0.0125,0.0078</t>
-  </si>
-  <si>
-    <t>0.9726,0.0041,0.0000,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0003,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9831,0.0038,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9994,0.0002</t>
-  </si>
-  <si>
-    <t>0.9913,0.0005,0.0001,0.0019</t>
-  </si>
-  <si>
-    <t>0.0021,0.0003,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0230,0.0101,0.9632,0.0056</t>
-  </si>
-  <si>
-    <t>0.1242,0.0005,0.8918,0.0051</t>
-  </si>
-  <si>
-    <t>0.4377,0.0032,0.6278,0.0011</t>
-  </si>
-  <si>
-    <t>0.0146,0.0006,0.9857,0.0005</t>
-  </si>
-  <si>
-    <t>0.0135,0.0001,0.9922,0.0001</t>
-  </si>
-  <si>
-    <t>0.1307,0.0007,0.8936,0.0019</t>
-  </si>
-  <si>
-    <t>0.3400,0.0066,0.6661,0.0205</t>
-  </si>
-  <si>
-    <t>0.8118,0.0013,0.2347,0.0019</t>
-  </si>
-  <si>
-    <t>0.8389,0.0019,0.0040,0.0606</t>
-  </si>
-  <si>
-    <t>0.8349,0.0124,0.1472,0.0026</t>
-  </si>
-  <si>
-    <t>0.8447,0.0206,0.1016,0.0008</t>
-  </si>
-  <si>
-    <t>0.7605,0.0045,0.2891,0.0012</t>
-  </si>
-  <si>
-    <t>0.8906,0.0003,0.0144,0.0375</t>
-  </si>
-  <si>
-    <t>0.9694,0.0008,0.0129,0.0026</t>
-  </si>
-  <si>
-    <t>0.1579,0.7167,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.0394,0.9468,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0981,0.8827,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9666,0.0119,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9587,0.0058,0.0001,0.0023</t>
-  </si>
-  <si>
-    <t>0.9466,0.0014,0.0245,0.0040</t>
-  </si>
-  <si>
-    <t>0.9939,0.0001,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.9455,0.0003,0.0067,0.0109</t>
-  </si>
-  <si>
-    <t>0.8183,0.0094,0.0888,0.0244</t>
-  </si>
-  <si>
-    <t>0.9863,0.0006,0.0030,0.0004</t>
-  </si>
-  <si>
-    <t>0.0346,0.0003,0.9663,0.0060</t>
-  </si>
-  <si>
-    <t>0.6930,0.0005,0.3201,0.0072</t>
-  </si>
-  <si>
-    <t>0.6332,0.0032,0.4265,0.0048</t>
-  </si>
-  <si>
-    <t>0.7439,0.0001,0.3138,0.0026</t>
-  </si>
-  <si>
-    <t>0.1698,0.1452,0.6295,0.0183</t>
-  </si>
-  <si>
-    <t>0.9939,0.0001,0.0000,0.0021</t>
-  </si>
-  <si>
-    <t>0.9888,0.0040,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9354,0.0017,0.0000,0.0140</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9803,0.0064,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0082,0.0012,0.9912,0.0014</t>
-  </si>
-  <si>
-    <t>0.6061,0.0223,0.1730,0.1041</t>
-  </si>
-  <si>
-    <t>0.9470,0.0008,0.0073,0.0163</t>
-  </si>
-  <si>
-    <t>0.0056,0.0004,0.9940,0.0004</t>
-  </si>
-  <si>
-    <t>0.0174,0.0002,0.9849,0.0004</t>
-  </si>
-  <si>
-    <t>0.1221,0.0052,0.8740,0.0019</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.2469,0.0003,0.8470,0.0005</t>
-  </si>
-  <si>
-    <t>0.0048,0.0007,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.4360,0.0013,0.6225,0.0038</t>
-  </si>
-  <si>
-    <t>0.6986,0.0007,0.0579,0.1038</t>
-  </si>
-  <si>
-    <t>0.8686,0.0019,0.1016,0.0075</t>
-  </si>
-  <si>
-    <t>0.9274,0.0002,0.0828,0.0012</t>
-  </si>
-  <si>
-    <t>0.9792,0.0004,0.0034,0.0028</t>
-  </si>
-  <si>
-    <t>0.9963,0.0001,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9979,0.0002,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0016,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9887,0.0002,0.0000,0.0027</t>
-  </si>
-  <si>
-    <t>0.9878,0.0002,0.0000,0.0041</t>
-  </si>
-  <si>
-    <t>0.3883,0.0083,0.6319,0.0012</t>
-  </si>
-  <si>
-    <t>0.2768,0.0006,0.8367,0.0001</t>
-  </si>
-  <si>
-    <t>0.2981,0.0388,0.6035,0.0024</t>
-  </si>
-  <si>
-    <t>0.4918,0.0764,0.3385,0.0108</t>
-  </si>
-  <si>
-    <t>0.0692,0.0001,0.9367,0.0020</t>
-  </si>
-  <si>
-    <t>0.2663,0.0002,0.4552,0.0731</t>
-  </si>
-  <si>
-    <t>0.6111,0.0000,0.1747,0.0301</t>
-  </si>
-  <si>
-    <t>0.9384,0.0002,0.0741,0.0006</t>
-  </si>
-  <si>
-    <t>0.9802,0.0000,0.0006,0.0128</t>
-  </si>
-  <si>
-    <t>0.2022,0.0004,0.0007,0.8815</t>
-  </si>
-  <si>
-    <t>0.0638,0.0001,0.0002,0.9829</t>
-  </si>
-  <si>
-    <t>0.0021,0.0000,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0022,0.0000,0.0001,0.9994</t>
-  </si>
-  <si>
-    <t>0.9879,0.0005,0.0009,0.0027</t>
+    <t>0.0151,0.2290,0.9392,0.0025</t>
+  </si>
+  <si>
+    <t>0.0527,0.3146,0.6721,0.0003</t>
+  </si>
+  <si>
+    <t>0.3747,0.0039,0.6918,0.0011</t>
+  </si>
+  <si>
+    <t>0.7892,0.0008,0.2771,0.0016</t>
+  </si>
+  <si>
+    <t>0.9730,0.0004,0.0070,0.0027</t>
+  </si>
+  <si>
+    <t>0.9886,0.0006,0.0026,0.0008</t>
+  </si>
+  <si>
+    <t>0.1863,0.0002,0.8260,0.0059</t>
+  </si>
+  <si>
+    <t>0.9536,0.0002,0.0136,0.0070</t>
+  </si>
+  <si>
+    <t>0.6540,0.0002,0.0000,0.2178</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0244,0.0003,0.0001,0.9927</t>
+  </si>
+  <si>
+    <t>0.0147,0.0000,0.0001,0.9966</t>
+  </si>
+  <si>
+    <t>0.0070,0.9335,0.5311,0.0021</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0107,0.9442,0.0001,0.0074</t>
+  </si>
+  <si>
+    <t>0.9495,0.0166,0.0004,0.0023</t>
+  </si>
+  <si>
+    <t>0.9964,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.4016,0.0000,0.0001,0.8100</t>
+  </si>
+  <si>
+    <t>0.2622,0.0058,0.7373,0.0160</t>
+  </si>
+  <si>
+    <t>0.9959,0.0001,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.8799,0.0162,0.0092,0.0219</t>
+  </si>
+  <si>
+    <t>0.9831,0.0020,0.0003,0.0025</t>
+  </si>
+  <si>
+    <t>0.9923,0.0015,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.7773,0.0125,0.0004,0.0290</t>
+  </si>
+  <si>
+    <t>0.9623,0.0079,0.0005,0.0029</t>
+  </si>
+  <si>
+    <t>0.9378,0.0022,0.0001,0.0092</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9977,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9852,0.0003,0.0000,0.0033</t>
+  </si>
+  <si>
+    <t>0.9422,0.0108,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9448,0.0148,0.0005,0.0035</t>
+  </si>
+  <si>
+    <t>0.9717,0.0092,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.1209,0.0065,0.8885,0.0074</t>
+  </si>
+  <si>
+    <t>0.9624,0.0045,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.9954,0.0003,0.0000,0.0008</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9828,0.0008,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0003,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0535,0.0058,0.9426,0.0025</t>
+  </si>
+  <si>
+    <t>0.7905,0.0004,0.1121,0.0224</t>
+  </si>
+  <si>
+    <t>0.6417,0.0033,0.4371,0.0009</t>
+  </si>
+  <si>
+    <t>0.0073,0.0016,0.9901,0.0010</t>
+  </si>
+  <si>
+    <t>0.1739,0.0001,0.9046,0.0004</t>
+  </si>
+  <si>
+    <t>0.0013,0.0003,0.9980,0.0006</t>
+  </si>
+  <si>
+    <t>0.5083,0.0021,0.5551,0.0075</t>
+  </si>
+  <si>
+    <t>0.2191,0.0020,0.8085,0.0061</t>
+  </si>
+  <si>
+    <t>0.9503,0.0005,0.0027,0.0113</t>
+  </si>
+  <si>
+    <t>0.8316,0.0094,0.1506,0.0045</t>
+  </si>
+  <si>
+    <t>0.5228,0.0310,0.4067,0.0024</t>
+  </si>
+  <si>
+    <t>0.6956,0.0046,0.3623,0.0013</t>
+  </si>
+  <si>
+    <t>0.9476,0.0006,0.0039,0.0119</t>
+  </si>
+  <si>
+    <t>0.8373,0.0005,0.0663,0.0305</t>
+  </si>
+  <si>
+    <t>0.3782,0.4051,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.0486,0.9319,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.8727,0.0931,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9788,0.0118,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.7465,0.0546,0.0001,0.0042</t>
+  </si>
+  <si>
+    <t>0.9822,0.0023,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.9935,0.0005,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9873,0.0003,0.0024,0.0008</t>
+  </si>
+  <si>
+    <t>0.9481,0.0016,0.0437,0.0008</t>
+  </si>
+  <si>
+    <t>0.9613,0.0006,0.0169,0.0034</t>
+  </si>
+  <si>
+    <t>0.0665,0.0005,0.9310,0.0070</t>
+  </si>
+  <si>
+    <t>0.6646,0.0003,0.3306,0.0066</t>
+  </si>
+  <si>
+    <t>0.6997,0.0095,0.2789,0.0163</t>
+  </si>
+  <si>
+    <t>0.8686,0.0001,0.1864,0.0008</t>
+  </si>
+  <si>
+    <t>0.1294,0.1507,0.6390,0.0066</t>
+  </si>
+  <si>
+    <t>0.9970,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9932,0.0018,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9698,0.0004,0.0000,0.0066</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9918,0.0026,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9972,0.0002,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.0112,0.0012,0.9904,0.0017</t>
+  </si>
+  <si>
+    <t>0.5015,0.1168,0.2372,0.0847</t>
+  </si>
+  <si>
+    <t>0.9451,0.0012,0.0053,0.0185</t>
+  </si>
+  <si>
+    <t>0.0358,0.0003,0.9797,0.0001</t>
+  </si>
+  <si>
+    <t>0.0163,0.0004,0.9864,0.0003</t>
+  </si>
+  <si>
+    <t>0.2189,0.0022,0.8199,0.0014</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.4835,0.0004,0.6158,0.0024</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0587,0.0005,0.9507,0.0004</t>
+  </si>
+  <si>
+    <t>0.1657,0.0020,0.8533,0.0050</t>
+  </si>
+  <si>
+    <t>0.9475,0.0003,0.0356,0.0029</t>
+  </si>
+  <si>
+    <t>0.9089,0.0005,0.1057,0.0018</t>
+  </si>
+  <si>
+    <t>0.9625,0.0005,0.0134,0.0046</t>
+  </si>
+  <si>
+    <t>0.9937,0.0002,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9942,0.0013,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9846,0.0003,0.0000,0.0041</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.5937,0.0109,0.4285,0.0019</t>
+  </si>
+  <si>
+    <t>0.0931,0.0052,0.9145,0.0002</t>
+  </si>
+  <si>
+    <t>0.2294,0.0771,0.4646,0.0007</t>
+  </si>
+  <si>
+    <t>0.3241,0.2253,0.2709,0.0141</t>
+  </si>
+  <si>
+    <t>0.0112,0.0002,0.9878,0.0005</t>
+  </si>
+  <si>
+    <t>0.8607,0.0002,0.0763,0.0126</t>
+  </si>
+  <si>
+    <t>0.3436,0.0002,0.5241,0.0288</t>
+  </si>
+  <si>
+    <t>0.7908,0.0002,0.2285,0.0036</t>
+  </si>
+  <si>
+    <t>0.9896,0.0001,0.0001,0.0062</t>
+  </si>
+  <si>
+    <t>0.8426,0.0005,0.0010,0.1056</t>
+  </si>
+  <si>
+    <t>0.0794,0.0000,0.0002,0.9788</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.0001,0.9996</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9096,0.0009,0.0003,0.0300</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1917,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1943,7 +1931,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1957,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1971,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1985,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1999,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2013,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2027,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2041,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2055,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2069,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2083,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2097,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2111,7 +2099,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2125,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2139,7 +2127,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2153,7 +2141,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2167,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2181,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2192,10 +2180,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2209,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2223,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2237,7 +2225,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2251,7 +2239,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2265,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2279,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2293,7 +2281,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2304,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2321,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2335,7 +2323,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2349,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2363,7 +2351,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2377,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2391,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2405,7 +2393,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2419,7 +2407,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2433,7 +2421,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2444,10 +2432,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2461,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2475,7 +2463,7 @@
         <v>259</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2489,7 +2477,7 @@
         <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2503,7 +2491,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2517,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2531,7 +2519,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2545,7 +2533,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2559,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2573,7 +2561,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2587,7 +2575,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2601,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2615,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2626,10 +2614,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2643,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2657,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2671,7 +2659,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2685,7 +2673,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2699,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2713,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2727,7 +2715,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2741,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2755,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2769,7 +2757,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2780,10 +2768,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2797,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2811,7 +2799,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2825,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2839,7 +2827,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2853,7 +2841,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2867,7 +2855,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2881,7 +2869,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2892,10 +2880,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2909,7 +2897,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2920,10 +2908,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2937,7 +2925,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2951,7 +2939,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2962,10 +2950,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2979,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2993,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3007,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3021,7 +3009,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3035,7 +3023,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3049,7 +3037,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3063,7 +3051,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3077,7 +3065,7 @@
         <v>262</v>
       </c>
       <c r="D84" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3091,7 +3079,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3105,7 +3093,7 @@
         <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3119,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3130,10 +3118,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D88" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3147,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>275</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3161,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3175,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>351</v>
+        <v>320</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3189,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3203,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3217,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3231,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3245,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3259,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3273,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3287,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3301,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3315,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3329,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3343,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3357,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>363</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3371,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3382,10 +3370,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3399,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3413,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3427,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3441,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3455,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3469,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3483,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3497,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3511,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3525,7 +3513,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3539,7 +3527,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3553,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3567,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3581,7 +3569,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3595,7 +3583,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3609,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3623,7 +3611,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3637,7 +3625,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3651,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3665,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3679,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3693,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3707,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>388</v>
+        <v>275</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3721,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3735,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>357</v>
+        <v>391</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3749,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3763,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3777,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3791,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3805,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3819,7 +3807,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3833,7 +3821,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3844,10 +3832,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D139" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3861,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3875,7 +3863,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3886,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3903,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3917,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3931,7 +3919,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3945,7 +3933,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3959,7 +3947,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3973,7 +3961,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3987,7 +3975,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4001,7 +3989,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4015,7 +4003,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>409</v>
+        <v>365</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4029,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4043,7 +4031,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4054,10 +4042,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4071,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4085,7 +4073,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4099,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4113,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4127,7 +4115,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4141,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4155,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4169,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4183,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4197,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4211,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>422</v>
+        <v>395</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4225,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>388</v>
+        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4267,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>425</v>
+        <v>355</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4281,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4295,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>427</v>
+        <v>273</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4309,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4323,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4337,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4351,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4362,10 +4350,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4379,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4393,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4407,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4421,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4435,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4449,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4463,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4477,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4488,10 +4476,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D185" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4502,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D186" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4519,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4533,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4547,7 +4535,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4558,10 +4546,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4572,10 +4560,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4589,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4603,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4617,7 +4605,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4631,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4645,7 +4633,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4659,7 +4647,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4670,10 +4658,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D198" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4687,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4698,10 +4686,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4715,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4729,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4743,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4757,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4771,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4785,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4799,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4813,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4827,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D209" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4841,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D210" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4855,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4869,7 +4857,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4883,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4897,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4911,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4925,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4939,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4953,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4967,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4981,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>275</v>
+        <v>391</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4995,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5009,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5023,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5037,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5051,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5065,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5079,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5093,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5107,7 +5095,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5121,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5132,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5149,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5163,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5177,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5191,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5205,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5219,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>491</v>
+        <v>277</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5233,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5247,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5261,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>493</v>
+        <v>395</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5275,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5289,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5300,10 +5288,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D243" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5317,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5328,10 +5316,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D245" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5342,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D246" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5359,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5373,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5384,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5401,7 +5389,7 @@
         <v>259</v>
       </c>
       <c r="D250" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5415,7 +5403,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5426,10 +5414,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D252" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5443,7 +5431,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5457,7 +5445,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5471,7 +5459,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5485,7 +5473,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
